--- a/artfynd/A 35514-2026 artfynd.xlsx
+++ b/artfynd/A 35514-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89738519</v>
+        <v>137016005</v>
       </c>
       <c r="B2" t="n">
-        <v>95957</v>
+        <v>96784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +691,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2383</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>utan kapsel</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lunnane, Dls</t>
+          <t>Lunnane, ca 350 m NNO om, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>335224</v>
+        <v>335284</v>
       </c>
       <c r="R2" t="n">
-        <v>6523820</v>
+        <v>6523983</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,58 +749,62 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Ödskölt</t>
+          <t>Bäcke</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt förekommande, dock inga kapslar och svårt att utesluta P. elatum.</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Gammal barrskog.</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>På murken granlåga.</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89738519</t>
+          <t>https://artportalen.se/Sighting/137016005</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89738521</v>
+        <v>137017302</v>
       </c>
       <c r="B3" t="n">
-        <v>96458</v>
+        <v>96185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,39 +812,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2818</v>
+        <v>2381</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bandpraktmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Plagiomnium elatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lunnane, Dls</t>
+          <t>Lunnane, NNO om, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>335273</v>
+        <v>335286</v>
       </c>
       <c r="R3" t="n">
-        <v>6523895</v>
+        <v>6523997</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,22 +861,17 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Bäcke</t>
+          <t>Ödskölt</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>på gammal granstubbe</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,80 +882,79 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Gammalt dike/bäck i gammal barrskog.</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89738521</t>
+          <t>https://artportalen.se/Sighting/137017302</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89738931</v>
+        <v>89738519</v>
       </c>
       <c r="B4" t="n">
-        <v>57966</v>
+        <v>95957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>2383</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lunnane, Bäckefors, Dls</t>
+          <t>Lunnane, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>335247</v>
+        <v>335224</v>
       </c>
       <c r="R4" t="n">
-        <v>6523803</v>
+        <v>6523820</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,35 +976,31 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Bäcke</t>
+          <t>Ödskölt</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:29</t>
+          <t>2020-09-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:29</t>
+          <t>2020-09-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt förekommande, dock inga kapslar och svårt att utesluta P. elatum.</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1028,16 +1018,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89738931</t>
+          <t>https://artportalen.se/Sighting/89738519</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89738935</v>
+        <v>137017303</v>
       </c>
       <c r="B5" t="n">
-        <v>97983</v>
+        <v>96192</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,44 +1035,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>2387</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lunnane, Bäckefors, Dls</t>
+          <t>Lunnane, NNO om, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>335228</v>
+        <v>335286</v>
       </c>
       <c r="R5" t="n">
-        <v>6523826</v>
+        <v>6523997</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,22 +1084,17 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Bäcke</t>
+          <t>Ödskölt</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>riklig</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,20 +1105,1684 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Gammalt dike/bäck i gammal barrskog.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137017303</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137017325</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96192</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2387</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Källpraktmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pseudobryum cinclidioides</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lunnane, NNO om, Dls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>335295</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6523992</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Gammalt dike/bäck i gammal barrskog.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137017325</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>89738521</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96458</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lunnane, Dls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>335273</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6523895</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-09-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-09-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>på gammal granstubbe</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89738521</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137015980</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96688</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lunnane, ca 350 m NNO om, Dls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>335284</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6523983</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Gammal barrskog.</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>På murken granlåga.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137015980</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137015946</v>
+      </c>
+      <c r="B9" t="n">
+        <v>75566</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lunnane, NNO om, Dls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>335295</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6524001</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Gammal barrskog.</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>På gammal gran.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137015946</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>89738931</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57966</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lunnane, Bäckefors, Dls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>335247</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6523803</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-09-22</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-09-22</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89738931</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137015925</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lunnane, NNO om, Dls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>335286</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6524004</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ödskölt</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>hackmärken gammal i gran</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Gammal barrskog.</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137015925</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137015976</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lunnane, NO-NNO om, Dls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>335315</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6524012</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>hackmärken gammal i gran</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Gammal barrskog.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137015976</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137015927</v>
+      </c>
+      <c r="B13" t="n">
+        <v>4777</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lunnane, NNO om, Dls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>335286</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6524004</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ödskölt</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Gammal barrskog.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137015927</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137015967</v>
+      </c>
+      <c r="B14" t="n">
+        <v>4777</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lunnane, 500 m NO om, Dls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>335458</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6524035</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Gammal barrskog.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137015967</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137015969</v>
+      </c>
+      <c r="B15" t="n">
+        <v>4777</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lunnane, ca 475 m NO om, Dls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>335426</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6524031</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Gammal barrskog.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137015969</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137015926</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5182</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lunnane, NNO om, Dls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>335286</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6524004</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ödskölt</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Gammal barrskog.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137015926</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137015970</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5182</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lunnane, ca 475 m NO om, Dls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>335426</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6524031</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Gammal barrskog.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137015970</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137016034</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5182</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lunnane, NO-NNO om, Dls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>335383</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6524056</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Gammal barrskog.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016034</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137015800</v>
+      </c>
+      <c r="B19" t="n">
+        <v>108378</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lunnane, NNO om, Dls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>335316</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6524096</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ödskölt</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Gammal barrskog.</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137015800</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>89738935</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lunnane, Bäckefors, Dls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>335228</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6523826</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2020-09-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2020-09-22</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>riklig</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/89738935</t>
         </is>
@@ -1155,6 +2794,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35514-2026 artfynd.xlsx
+++ b/artfynd/A 35514-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137016005</v>
       </c>
       <c r="B2" t="n">
-        <v>96784</v>
+        <v>96790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137017302</v>
       </c>
       <c r="B3" t="n">
-        <v>96185</v>
+        <v>96191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137017303</v>
       </c>
       <c r="B5" t="n">
-        <v>96192</v>
+        <v>96198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>137017325</v>
       </c>
       <c r="B6" t="n">
-        <v>96192</v>
+        <v>96198</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>137015980</v>
       </c>
       <c r="B8" t="n">
-        <v>96688</v>
+        <v>96694</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>137015800</v>
       </c>
       <c r="B19" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35514-2026 artfynd.xlsx
+++ b/artfynd/A 35514-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137016005</v>
       </c>
       <c r="B2" t="n">
-        <v>96790</v>
+        <v>96792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137017302</v>
       </c>
       <c r="B3" t="n">
-        <v>96191</v>
+        <v>96193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137017303</v>
       </c>
       <c r="B5" t="n">
-        <v>96198</v>
+        <v>96200</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>137017325</v>
       </c>
       <c r="B6" t="n">
-        <v>96198</v>
+        <v>96200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>137015980</v>
       </c>
       <c r="B8" t="n">
-        <v>96694</v>
+        <v>96696</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>137015800</v>
       </c>
       <c r="B19" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35514-2026 artfynd.xlsx
+++ b/artfynd/A 35514-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137016005</v>
       </c>
       <c r="B2" t="n">
-        <v>96792</v>
+        <v>96793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137017302</v>
       </c>
       <c r="B3" t="n">
-        <v>96193</v>
+        <v>96194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137017303</v>
       </c>
       <c r="B5" t="n">
-        <v>96200</v>
+        <v>96201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>137017325</v>
       </c>
       <c r="B6" t="n">
-        <v>96200</v>
+        <v>96201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>137015980</v>
       </c>
       <c r="B8" t="n">
-        <v>96696</v>
+        <v>96697</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>137015800</v>
       </c>
       <c r="B19" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35514-2026 artfynd.xlsx
+++ b/artfynd/A 35514-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137016005</v>
       </c>
       <c r="B2" t="n">
-        <v>96793</v>
+        <v>96799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137017302</v>
       </c>
       <c r="B3" t="n">
-        <v>96194</v>
+        <v>96200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137017303</v>
       </c>
       <c r="B5" t="n">
-        <v>96201</v>
+        <v>96207</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>137017325</v>
       </c>
       <c r="B6" t="n">
-        <v>96201</v>
+        <v>96207</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>137015980</v>
       </c>
       <c r="B8" t="n">
-        <v>96697</v>
+        <v>96703</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>137015800</v>
       </c>
       <c r="B19" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35514-2026 artfynd.xlsx
+++ b/artfynd/A 35514-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137016005</v>
       </c>
       <c r="B2" t="n">
-        <v>96799</v>
+        <v>96803</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137017302</v>
       </c>
       <c r="B3" t="n">
-        <v>96200</v>
+        <v>96204</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137017303</v>
       </c>
       <c r="B5" t="n">
-        <v>96207</v>
+        <v>96211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>137017325</v>
       </c>
       <c r="B6" t="n">
-        <v>96207</v>
+        <v>96211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>137015980</v>
       </c>
       <c r="B8" t="n">
-        <v>96703</v>
+        <v>96707</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>137015800</v>
       </c>
       <c r="B19" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35514-2026 artfynd.xlsx
+++ b/artfynd/A 35514-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137016005</v>
       </c>
       <c r="B2" t="n">
-        <v>96803</v>
+        <v>96805</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137017302</v>
       </c>
       <c r="B3" t="n">
-        <v>96204</v>
+        <v>96206</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137017303</v>
       </c>
       <c r="B5" t="n">
-        <v>96211</v>
+        <v>96213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>137017325</v>
       </c>
       <c r="B6" t="n">
-        <v>96211</v>
+        <v>96213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>137015980</v>
       </c>
       <c r="B8" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>137015800</v>
       </c>
       <c r="B19" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35514-2026 artfynd.xlsx
+++ b/artfynd/A 35514-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137016005</v>
       </c>
       <c r="B2" t="n">
-        <v>96805</v>
+        <v>96807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137017302</v>
       </c>
       <c r="B3" t="n">
-        <v>96206</v>
+        <v>96208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137017303</v>
       </c>
       <c r="B5" t="n">
-        <v>96213</v>
+        <v>96215</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>137017325</v>
       </c>
       <c r="B6" t="n">
-        <v>96213</v>
+        <v>96215</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>137015980</v>
       </c>
       <c r="B8" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>137015800</v>
       </c>
       <c r="B19" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35514-2026 artfynd.xlsx
+++ b/artfynd/A 35514-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137016005</v>
       </c>
       <c r="B2" t="n">
-        <v>96807</v>
+        <v>96820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137017302</v>
       </c>
       <c r="B3" t="n">
-        <v>96208</v>
+        <v>96221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137017303</v>
       </c>
       <c r="B5" t="n">
-        <v>96215</v>
+        <v>96228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>137017325</v>
       </c>
       <c r="B6" t="n">
-        <v>96215</v>
+        <v>96228</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>137015980</v>
       </c>
       <c r="B8" t="n">
-        <v>96711</v>
+        <v>96724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>137015946</v>
       </c>
       <c r="B9" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137015925</v>
       </c>
       <c r="B11" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137015976</v>
       </c>
       <c r="B12" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>137015800</v>
       </c>
       <c r="B19" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35514-2026 artfynd.xlsx
+++ b/artfynd/A 35514-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137016005</v>
       </c>
       <c r="B2" t="n">
-        <v>96820</v>
+        <v>96822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137017302</v>
       </c>
       <c r="B3" t="n">
-        <v>96221</v>
+        <v>96223</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137017303</v>
       </c>
       <c r="B5" t="n">
-        <v>96228</v>
+        <v>96230</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>137017325</v>
       </c>
       <c r="B6" t="n">
-        <v>96228</v>
+        <v>96230</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>137015980</v>
       </c>
       <c r="B8" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>137015946</v>
       </c>
       <c r="B9" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137015925</v>
       </c>
       <c r="B11" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137015976</v>
       </c>
       <c r="B12" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>137015800</v>
       </c>
       <c r="B19" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35514-2026 artfynd.xlsx
+++ b/artfynd/A 35514-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137016005</v>
       </c>
       <c r="B2" t="n">
-        <v>96822</v>
+        <v>96825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137017302</v>
       </c>
       <c r="B3" t="n">
-        <v>96223</v>
+        <v>96226</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137017303</v>
       </c>
       <c r="B5" t="n">
-        <v>96230</v>
+        <v>96233</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>137017325</v>
       </c>
       <c r="B6" t="n">
-        <v>96230</v>
+        <v>96233</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>137015980</v>
       </c>
       <c r="B8" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>137015800</v>
       </c>
       <c r="B19" t="n">
-        <v>108416</v>
+        <v>108421</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35514-2026 artfynd.xlsx
+++ b/artfynd/A 35514-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137016005</v>
       </c>
       <c r="B2" t="n">
-        <v>96825</v>
+        <v>96835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137017302</v>
       </c>
       <c r="B3" t="n">
-        <v>96226</v>
+        <v>96236</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137017303</v>
       </c>
       <c r="B5" t="n">
-        <v>96233</v>
+        <v>96243</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>137017325</v>
       </c>
       <c r="B6" t="n">
-        <v>96233</v>
+        <v>96243</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>137015980</v>
       </c>
       <c r="B8" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>137015946</v>
       </c>
       <c r="B9" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137015925</v>
       </c>
       <c r="B11" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137015976</v>
       </c>
       <c r="B12" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137015927</v>
       </c>
       <c r="B13" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>137015967</v>
       </c>
       <c r="B14" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>137015969</v>
       </c>
       <c r="B15" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>137015926</v>
       </c>
       <c r="B16" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>137015970</v>
       </c>
       <c r="B17" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>137016034</v>
       </c>
       <c r="B18" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>137015800</v>
       </c>
       <c r="B19" t="n">
-        <v>108421</v>
+        <v>108442</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35514-2026 artfynd.xlsx
+++ b/artfynd/A 35514-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137016005</v>
       </c>
       <c r="B2" t="n">
-        <v>96835</v>
+        <v>96836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137017302</v>
       </c>
       <c r="B3" t="n">
-        <v>96236</v>
+        <v>96237</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137017303</v>
       </c>
       <c r="B5" t="n">
-        <v>96243</v>
+        <v>96244</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>137017325</v>
       </c>
       <c r="B6" t="n">
-        <v>96243</v>
+        <v>96244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>137015980</v>
       </c>
       <c r="B8" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>137015800</v>
       </c>
       <c r="B19" t="n">
-        <v>108442</v>
+        <v>108443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35514-2026 artfynd.xlsx
+++ b/artfynd/A 35514-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137016005</v>
       </c>
       <c r="B2" t="n">
-        <v>96836</v>
+        <v>96841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137017302</v>
       </c>
       <c r="B3" t="n">
-        <v>96237</v>
+        <v>96242</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137017303</v>
       </c>
       <c r="B5" t="n">
-        <v>96244</v>
+        <v>96249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>137017325</v>
       </c>
       <c r="B6" t="n">
-        <v>96244</v>
+        <v>96249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>137015980</v>
       </c>
       <c r="B8" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>137015946</v>
       </c>
       <c r="B9" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137015925</v>
       </c>
       <c r="B11" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137015976</v>
       </c>
       <c r="B12" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>137015800</v>
       </c>
       <c r="B19" t="n">
-        <v>108443</v>
+        <v>108448</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35514-2026 artfynd.xlsx
+++ b/artfynd/A 35514-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137016005</v>
       </c>
       <c r="B2" t="n">
-        <v>96841</v>
+        <v>96843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137017302</v>
       </c>
       <c r="B3" t="n">
-        <v>96242</v>
+        <v>96244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137017303</v>
       </c>
       <c r="B5" t="n">
-        <v>96249</v>
+        <v>96251</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>137017325</v>
       </c>
       <c r="B6" t="n">
-        <v>96249</v>
+        <v>96251</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>137015980</v>
       </c>
       <c r="B8" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>137015800</v>
       </c>
       <c r="B19" t="n">
-        <v>108448</v>
+        <v>108451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35514-2026 artfynd.xlsx
+++ b/artfynd/A 35514-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137016005</v>
       </c>
       <c r="B2" t="n">
-        <v>96843</v>
+        <v>96849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137017302</v>
       </c>
       <c r="B3" t="n">
-        <v>96244</v>
+        <v>96250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137017303</v>
       </c>
       <c r="B5" t="n">
-        <v>96251</v>
+        <v>96257</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>137017325</v>
       </c>
       <c r="B6" t="n">
-        <v>96251</v>
+        <v>96257</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>137015980</v>
       </c>
       <c r="B8" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>137015946</v>
       </c>
       <c r="B9" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137015925</v>
       </c>
       <c r="B11" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137015976</v>
       </c>
       <c r="B12" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>137015800</v>
       </c>
       <c r="B19" t="n">
-        <v>108451</v>
+        <v>108457</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35514-2026 artfynd.xlsx
+++ b/artfynd/A 35514-2026 artfynd.xlsx
@@ -2569,7 +2569,7 @@
         <v>137015800</v>
       </c>
       <c r="B19" t="n">
-        <v>108457</v>
+        <v>108458</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35514-2026 artfynd.xlsx
+++ b/artfynd/A 35514-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137016005</v>
       </c>
       <c r="B2" t="n">
-        <v>96849</v>
+        <v>96861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137017302</v>
       </c>
       <c r="B3" t="n">
-        <v>96250</v>
+        <v>96262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137017303</v>
       </c>
       <c r="B5" t="n">
-        <v>96257</v>
+        <v>96269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>137017325</v>
       </c>
       <c r="B6" t="n">
-        <v>96257</v>
+        <v>96269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>137015980</v>
       </c>
       <c r="B8" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>137015946</v>
       </c>
       <c r="B9" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>137015800</v>
       </c>
       <c r="B19" t="n">
-        <v>108458</v>
+        <v>108470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35514-2026 artfynd.xlsx
+++ b/artfynd/A 35514-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137016005</v>
       </c>
       <c r="B2" t="n">
-        <v>96861</v>
+        <v>96862</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137017302</v>
       </c>
       <c r="B3" t="n">
-        <v>96262</v>
+        <v>96263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137017303</v>
       </c>
       <c r="B5" t="n">
-        <v>96269</v>
+        <v>96270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>137017325</v>
       </c>
       <c r="B6" t="n">
-        <v>96269</v>
+        <v>96270</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>137015980</v>
       </c>
       <c r="B8" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>137015800</v>
       </c>
       <c r="B19" t="n">
-        <v>108470</v>
+        <v>108471</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35514-2026 artfynd.xlsx
+++ b/artfynd/A 35514-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137016005</v>
       </c>
       <c r="B2" t="n">
-        <v>96862</v>
+        <v>96865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137017302</v>
       </c>
       <c r="B3" t="n">
-        <v>96263</v>
+        <v>96266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137017303</v>
       </c>
       <c r="B5" t="n">
-        <v>96270</v>
+        <v>96273</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>137017325</v>
       </c>
       <c r="B6" t="n">
-        <v>96270</v>
+        <v>96273</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>137015980</v>
       </c>
       <c r="B8" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>137015800</v>
       </c>
       <c r="B19" t="n">
-        <v>108471</v>
+        <v>108474</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35514-2026 artfynd.xlsx
+++ b/artfynd/A 35514-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137016005</v>
       </c>
       <c r="B2" t="n">
-        <v>96865</v>
+        <v>96866</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137017302</v>
       </c>
       <c r="B3" t="n">
-        <v>96266</v>
+        <v>96267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137017303</v>
       </c>
       <c r="B5" t="n">
-        <v>96273</v>
+        <v>96274</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>137017325</v>
       </c>
       <c r="B6" t="n">
-        <v>96273</v>
+        <v>96274</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>137015980</v>
       </c>
       <c r="B8" t="n">
-        <v>96769</v>
+        <v>96770</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>137015946</v>
       </c>
       <c r="B9" t="n">
-        <v>75610</v>
+        <v>75611</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>137015800</v>
       </c>
       <c r="B19" t="n">
-        <v>108474</v>
+        <v>108476</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35514-2026 artfynd.xlsx
+++ b/artfynd/A 35514-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137016005</v>
       </c>
       <c r="B2" t="n">
-        <v>96866</v>
+        <v>96869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137017302</v>
       </c>
       <c r="B3" t="n">
-        <v>96267</v>
+        <v>96270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137017303</v>
       </c>
       <c r="B5" t="n">
-        <v>96274</v>
+        <v>96277</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>137017325</v>
       </c>
       <c r="B6" t="n">
-        <v>96274</v>
+        <v>96277</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>137015980</v>
       </c>
       <c r="B8" t="n">
-        <v>96770</v>
+        <v>96773</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>137015946</v>
       </c>
       <c r="B9" t="n">
-        <v>75611</v>
+        <v>75614</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137015925</v>
       </c>
       <c r="B11" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137015976</v>
       </c>
       <c r="B12" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>137015800</v>
       </c>
       <c r="B19" t="n">
-        <v>108476</v>
+        <v>108480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
